--- a/results/gmac_snr6dB/gmac_snr6dB_classC_Ru23_Rv46_SC/classC_Ru23_Rv46_snr6dB_SC.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classC_Ru23_Rv46_SC/classC_Ru23_Rv46_snr6dB_SC.xlsx
@@ -473,7 +473,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gaussian MAC — Class C, (Ru=0.23, Rv=0.46), SNR=6dB, SC (L=1), analytic design</t>
+          <t>Gaussian MAC — Class C, (Ru=0.23, Rv=0.46), SNR=6dB, SC (L=1)</t>
         </is>
       </c>
     </row>

--- a/results/gmac_snr6dB/gmac_snr6dB_classC_Ru23_Rv46_SC/classC_Ru23_Rv46_snr6dB_SC.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classC_Ru23_Rv46_SC/classC_Ru23_Rv46_snr6dB_SC.xlsx
@@ -676,10 +676,10 @@
         <v>0.6875</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.001</v>
+        <v>0.00175</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         <v>0.6875</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="12">
@@ -728,10 +728,10 @@
         <v>0.6885</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="14">
